--- a/Assets/Originals/Excels/DifficultyLevelExplanation/DifficultyLevelExplanation.xlsx
+++ b/Assets/Originals/Excels/DifficultyLevelExplanation/DifficultyLevelExplanation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\DifficultyLevelExplanation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47BE45B9-7542-4B85-ABF7-CB0982E2330A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AAF8F5E-259C-4754-BA24-82C4A8EBC4C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,21 +31,19 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>初心者向けの難易度です。
-3Dアクションが苦手な方でも楽しめるでしょう。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>中級者向けの難易度です。
-歯ごたえのある通常の難易度となっています。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>上級者向けの難易度です。</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>explanation</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>歯ごたえのある中級者向けの難易度。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3Dアクションが苦手な方でも楽しめる初心者向けの難易度。</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -385,7 +383,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -393,20 +391,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="37.5">
+    <row r="3" spans="1:2">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="37.5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -414,7 +412,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:2">

--- a/Assets/Originals/Excels/DifficultyLevelExplanation/DifficultyLevelExplanation.xlsx
+++ b/Assets/Originals/Excels/DifficultyLevelExplanation/DifficultyLevelExplanation.xlsx
@@ -8,24 +8,35 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\DifficultyLevelExplanation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AAF8F5E-259C-4754-BA24-82C4A8EBC4C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8829A4B5-63BD-4627-970F-7B43D896061E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="difficultyLevelExplanation" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -44,6 +55,30 @@
   </si>
   <si>
     <t>3Dアクションが苦手な方でも楽しめる初心者向けの難易度。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>explanationSizeJapanese</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>explanationEnglish</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>explanationSizeEnglish</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>This game has a beginner-friendly difficulty level, making it enjoyable even for those who aren't good at 3D action games.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A challenging difficulty level suitable for intermediate players.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>This is an advanced level of difficulty.</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -372,50 +407,89 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="57.375" customWidth="1"/>
+    <col min="3" max="3" width="21.875" customWidth="1"/>
+    <col min="4" max="4" width="57.75" customWidth="1"/>
+    <col min="5" max="5" width="20.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>2</v>
       </c>
+      <c r="C1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="C3">
+        <v>14</v>
+      </c>
+      <c r="D3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3">
+        <v>10</v>
+      </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:5">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="C4">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4">
+        <v>14</v>
+      </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:5">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
         <v>1</v>
       </c>
+      <c r="C5">
+        <v>14</v>
+      </c>
+      <c r="D5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5">
+        <v>14</v>
+      </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:5">
       <c r="A6">
         <v>4</v>
       </c>

--- a/Assets/Originals/Excels/DifficultyLevelExplanation/DifficultyLevelExplanation.xlsx
+++ b/Assets/Originals/Excels/DifficultyLevelExplanation/DifficultyLevelExplanation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\DifficultyLevelExplanation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8829A4B5-63BD-4627-970F-7B43D896061E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7878A30-9ED7-4FF9-8377-6339BD3E969C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,22 +42,10 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>上級者向けの難易度です。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>explanation</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>歯ごたえのある中級者向けの難易度。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>3Dアクションが苦手な方でも楽しめる初心者向けの難易度。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>explanationSizeJapanese</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -78,7 +66,19 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>This is an advanced level of difficulty.</t>
+    <t>3Dアクションが&lt;r="とくい"&gt;得意&lt;/r&gt;な&lt;r="かた"&gt;方&lt;/r&gt;でも&lt;r="むずか"&gt;難&lt;/r&gt;しいと&lt;r="かん"&gt;感&lt;/r&gt;じる&lt;r="じょうきゅうしゃ"&gt;上級者&lt;/r&gt;&lt;r="む"&gt;向&lt;/r&gt;けの&lt;r="なんいど"&gt;難易度&lt;/r&gt;。&lt;r="ちょうせん"&gt;挑戦&lt;/r&gt;したことを&lt;r="こうかい"&gt;後悔&lt;/r&gt;することになるでしょう。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">A difficulty level for advanced players, one that even those skilled at 3D action games will find challenging. You'll come to regret ever attempting it. </t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3Dアクションが&lt;r="にがて"&gt;苦手&lt;/r&gt;な&lt;r="かた"&gt;方&lt;/r&gt;でも&lt;r="たの"&gt;楽&lt;/r&gt;しめる&lt;r="しょしんしゃ"&gt;初心者&lt;/r&gt;&lt;r="む"&gt;向&lt;/r&gt;けの&lt;r="なんいど"&gt;難易度&lt;/r&gt;。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;r="は"&gt;歯&lt;/r&gt;ごたえのある&lt;r="ちゅうきゅうしゃ"&gt;中級者&lt;/r&gt;&lt;r="む"&gt;向&lt;/r&gt;けの&lt;r="なんいど"&gt;難易度&lt;/r&gt;。</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -410,9 +410,9 @@
   <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="2" max="2" width="57.375" customWidth="1"/>
+    <col min="2" max="2" width="57.375" style="1" customWidth="1"/>
     <col min="3" max="3" width="21.875" customWidth="1"/>
-    <col min="4" max="4" width="57.75" customWidth="1"/>
+    <col min="4" max="4" width="57.75" style="1" customWidth="1"/>
     <col min="5" max="5" width="20.5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -420,17 +420,17 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" t="s">
-        <v>6</v>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -438,52 +438,52 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" ht="56.25">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C3">
         <v>14</v>
       </c>
-      <c r="D3" t="s">
-        <v>8</v>
+      <c r="D3" s="1" t="s">
+        <v>5</v>
       </c>
       <c r="E3">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" ht="37.5">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C4">
         <v>14</v>
       </c>
-      <c r="D4" t="s">
-        <v>9</v>
+      <c r="D4" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="E4">
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" ht="147.75" customHeight="1">
       <c r="A5">
         <v>3</v>
       </c>
-      <c r="B5" t="s">
-        <v>1</v>
+      <c r="B5" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="C5">
         <v>14</v>
       </c>
-      <c r="D5" t="s">
-        <v>10</v>
+      <c r="D5" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="E5">
         <v>14</v>

--- a/Assets/Originals/Excels/DifficultyLevelExplanation/DifficultyLevelExplanation.xlsx
+++ b/Assets/Originals/Excels/DifficultyLevelExplanation/DifficultyLevelExplanation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\DifficultyLevelExplanation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7878A30-9ED7-4FF9-8377-6339BD3E969C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80A48BF7-BF0D-4D0D-A2C0-84F4536646AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -79,6 +79,23 @@
   </si>
   <si>
     <t>&lt;r="は"&gt;歯&lt;/r&gt;ごたえのある&lt;r="ちゅうきゅうしゃ"&gt;中級者&lt;/r&gt;&lt;r="む"&gt;向&lt;/r&gt;けの&lt;r="なんいど"&gt;難易度&lt;/r&gt;。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>即使不擅长3D动作游戏的玩家也能享受的新手向难度。</t>
+  </si>
+  <si>
+    <t>具有一定挑战性的中级玩家向难度。</t>
+  </si>
+  <si>
+    <t>即使是擅长3D动作游戏的玩家也会感到困难的高级玩家向难度。你将会后悔挑战了它。</t>
+  </si>
+  <si>
+    <t>explanationChinese01</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>explanationSizeChinese01</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -86,7 +103,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -100,6 +117,12 @@
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -122,11 +145,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -407,16 +434,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="57.375" style="1" customWidth="1"/>
     <col min="3" max="3" width="21.875" customWidth="1"/>
     <col min="4" max="4" width="57.75" style="1" customWidth="1"/>
     <col min="5" max="5" width="20.5" customWidth="1"/>
+    <col min="6" max="6" width="21.375" customWidth="1"/>
+    <col min="7" max="7" width="23.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -432,13 +461,19 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="56.25">
+    <row r="3" spans="1:7" ht="100.5">
       <c r="A3">
         <v>1</v>
       </c>
@@ -454,8 +489,14 @@
       <c r="E3">
         <v>10</v>
       </c>
+      <c r="F3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="3">
+        <v>14</v>
+      </c>
     </row>
-    <row r="4" spans="1:5" ht="37.5">
+    <row r="4" spans="1:7" ht="67.5">
       <c r="A4">
         <v>2</v>
       </c>
@@ -471,8 +512,14 @@
       <c r="E4">
         <v>14</v>
       </c>
+      <c r="F4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="3">
+        <v>14</v>
+      </c>
     </row>
-    <row r="5" spans="1:5" ht="147.75" customHeight="1">
+    <row r="5" spans="1:7" ht="147.75" customHeight="1">
       <c r="A5">
         <v>3</v>
       </c>
@@ -488,8 +535,14 @@
       <c r="E5">
         <v>14</v>
       </c>
+      <c r="F5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="3">
+        <v>14</v>
+      </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>4</v>
       </c>

--- a/Assets/Originals/Excels/DifficultyLevelExplanation/DifficultyLevelExplanation.xlsx
+++ b/Assets/Originals/Excels/DifficultyLevelExplanation/DifficultyLevelExplanation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\DifficultyLevelExplanation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80A48BF7-BF0D-4D0D-A2C0-84F4536646AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78838981-2002-4C9D-A9DA-8BDE0A8F9A94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -96,6 +96,23 @@
   </si>
   <si>
     <t>explanationSizeChinese01</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>即使不擅長3D動作遊戲的玩家也能享受的新手向難度。</t>
+  </si>
+  <si>
+    <t>具有一定挑戰性的中級玩家向難度。</t>
+  </si>
+  <si>
+    <t>即使是擅長3D動作遊戲的玩家也會感到困難的高階玩家向難度。你將會後悔挑戰了它。</t>
+  </si>
+  <si>
+    <t>explanationChinese02</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>explanationSizeChinese02</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -103,7 +120,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -123,6 +140,12 @@
       <name val="Microsoft YaHei"/>
       <family val="2"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Microsoft JhengHei"/>
+      <family val="2"/>
+      <charset val="136"/>
     </font>
   </fonts>
   <fills count="2">
@@ -145,7 +168,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -154,6 +177,10 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -434,7 +461,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="57.375" style="1" customWidth="1"/>
@@ -443,9 +470,11 @@
     <col min="5" max="5" width="20.5" customWidth="1"/>
     <col min="6" max="6" width="21.375" customWidth="1"/>
     <col min="7" max="7" width="23.625" customWidth="1"/>
+    <col min="8" max="8" width="20.5" customWidth="1"/>
+    <col min="9" max="9" width="23.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:9" ht="56.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -467,13 +496,19 @@
       <c r="G1" t="s">
         <v>15</v>
       </c>
+      <c r="H1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I1" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:9">
       <c r="A2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="100.5">
+    <row r="3" spans="1:9" ht="92.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -495,8 +530,14 @@
       <c r="G3" s="3">
         <v>14</v>
       </c>
+      <c r="H3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" s="5">
+        <v>14</v>
+      </c>
     </row>
-    <row r="4" spans="1:7" ht="67.5">
+    <row r="4" spans="1:9" ht="62.25">
       <c r="A4">
         <v>2</v>
       </c>
@@ -518,8 +559,14 @@
       <c r="G4" s="3">
         <v>14</v>
       </c>
+      <c r="H4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" s="5">
+        <v>14</v>
+      </c>
     </row>
-    <row r="5" spans="1:7" ht="147.75" customHeight="1">
+    <row r="5" spans="1:9" ht="147.75" customHeight="1">
       <c r="A5">
         <v>3</v>
       </c>
@@ -541,8 +588,14 @@
       <c r="G5" s="3">
         <v>14</v>
       </c>
+      <c r="H5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I5" s="5">
+        <v>14</v>
+      </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:9">
       <c r="A6">
         <v>4</v>
       </c>

--- a/Assets/Originals/Excels/DifficultyLevelExplanation/DifficultyLevelExplanation.xlsx
+++ b/Assets/Originals/Excels/DifficultyLevelExplanation/DifficultyLevelExplanation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\DifficultyLevelExplanation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78838981-2002-4C9D-A9DA-8BDE0A8F9A94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BC66311-C71A-4BB8-B9EA-376BDBAD6797}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -114,6 +114,21 @@
   <si>
     <t>explanationSizeChinese02</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>explanationSpanish</t>
+  </si>
+  <si>
+    <t>explanationSizeSpanish</t>
+  </si>
+  <si>
+    <t>Un nivel de dificultad para principiantes, pensado para que incluso quienes no dominan los juegos de acción en 3D puedan disfrutarlo.</t>
+  </si>
+  <si>
+    <t>Un nivel de dificultad intermedio con un desafío considerable.</t>
+  </si>
+  <si>
+    <t>Un nivel de dificultad para expertos que resultará difícil incluso para quienes dominan los juegos de acción en 3D. Te arrepentirás de haberlo intentado.</t>
   </si>
 </sst>
 </file>
@@ -168,7 +183,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -181,6 +196,10 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -461,7 +480,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="57.375" style="1" customWidth="1"/>
@@ -472,9 +491,11 @@
     <col min="7" max="7" width="23.625" customWidth="1"/>
     <col min="8" max="8" width="20.5" customWidth="1"/>
     <col min="9" max="9" width="23.625" customWidth="1"/>
+    <col min="10" max="10" width="22.5" customWidth="1"/>
+    <col min="11" max="11" width="21.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="56.25">
+    <row r="1" spans="1:11" ht="56.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -502,13 +523,21 @@
       <c r="I1" t="s">
         <v>20</v>
       </c>
+      <c r="J1" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:11">
       <c r="A2">
         <v>0</v>
       </c>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
     </row>
-    <row r="3" spans="1:9" ht="92.25">
+    <row r="3" spans="1:11" ht="356.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -536,8 +565,14 @@
       <c r="I3" s="5">
         <v>14</v>
       </c>
+      <c r="J3" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="K3" s="6">
+        <v>10</v>
+      </c>
     </row>
-    <row r="4" spans="1:9" ht="62.25">
+    <row r="4" spans="1:11" ht="150">
       <c r="A4">
         <v>2</v>
       </c>
@@ -565,8 +600,14 @@
       <c r="I4" s="5">
         <v>14</v>
       </c>
+      <c r="J4" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K4" s="6">
+        <v>14</v>
+      </c>
     </row>
-    <row r="5" spans="1:9" ht="147.75" customHeight="1">
+    <row r="5" spans="1:11" ht="147.75" customHeight="1">
       <c r="A5">
         <v>3</v>
       </c>
@@ -594,8 +635,14 @@
       <c r="I5" s="5">
         <v>14</v>
       </c>
+      <c r="J5" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K5" s="6">
+        <v>14</v>
+      </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:11">
       <c r="A6">
         <v>4</v>
       </c>

--- a/Assets/Originals/Excels/DifficultyLevelExplanation/DifficultyLevelExplanation.xlsx
+++ b/Assets/Originals/Excels/DifficultyLevelExplanation/DifficultyLevelExplanation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\DifficultyLevelExplanation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BC66311-C71A-4BB8-B9EA-376BDBAD6797}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F54EAC7F-0400-48D6-BA85-9532BB02D00E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -129,6 +129,21 @@
   </si>
   <si>
     <t>Un nivel de dificultad para expertos que resultará difícil incluso para quienes dominan los juegos de acción en 3D. Te arrepentirás de haberlo intentado.</t>
+  </si>
+  <si>
+    <t>explanationPortuguese</t>
+  </si>
+  <si>
+    <t>explanationSizePortuguese</t>
+  </si>
+  <si>
+    <t>Um nível de dificuldade para iniciantes, pensado para que até quem não é bom em jogos de ação 3D possa se divertir.</t>
+  </si>
+  <si>
+    <t>Um nível de dificuldade intermediário com um desafio considerável.</t>
+  </si>
+  <si>
+    <t>Um nível de dificuldade para jogadores avançados, que será difícil até para quem domina jogos de ação 3D. Você vai se arrepender de ter tentado.</t>
   </si>
 </sst>
 </file>
@@ -480,7 +495,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="57.375" style="1" customWidth="1"/>
@@ -493,9 +508,11 @@
     <col min="9" max="9" width="23.625" customWidth="1"/>
     <col min="10" max="10" width="22.5" customWidth="1"/>
     <col min="11" max="11" width="21.25" customWidth="1"/>
+    <col min="12" max="12" width="22.25" customWidth="1"/>
+    <col min="13" max="13" width="24.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="56.25">
+    <row r="1" spans="1:13" ht="56.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -523,21 +540,27 @@
       <c r="I1" t="s">
         <v>20</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="K1" t="s">
         <v>22</v>
       </c>
+      <c r="L1" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M1" s="6" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:13">
       <c r="A2">
         <v>0</v>
       </c>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
     </row>
-    <row r="3" spans="1:11" ht="356.25">
+    <row r="3" spans="1:13" ht="262.5">
       <c r="A3">
         <v>1</v>
       </c>
@@ -565,14 +588,20 @@
       <c r="I3" s="5">
         <v>14</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="K3" s="6">
+      <c r="K3">
         <v>10</v>
       </c>
+      <c r="L3" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="M3" s="6">
+        <v>10</v>
+      </c>
     </row>
-    <row r="4" spans="1:11" ht="150">
+    <row r="4" spans="1:13" ht="187.5">
       <c r="A4">
         <v>2</v>
       </c>
@@ -600,14 +629,20 @@
       <c r="I4" s="5">
         <v>14</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="J4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="K4" s="6">
+      <c r="K4">
+        <v>14</v>
+      </c>
+      <c r="L4" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="M4" s="6">
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="147.75" customHeight="1">
+    <row r="5" spans="1:13" ht="147.75" customHeight="1">
       <c r="A5">
         <v>3</v>
       </c>
@@ -635,14 +670,20 @@
       <c r="I5" s="5">
         <v>14</v>
       </c>
-      <c r="J5" s="7" t="s">
+      <c r="J5" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K5" s="6">
+      <c r="K5">
+        <v>14</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="M5" s="6">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:13">
       <c r="A6">
         <v>4</v>
       </c>

--- a/Assets/Originals/Excels/DifficultyLevelExplanation/DifficultyLevelExplanation.xlsx
+++ b/Assets/Originals/Excels/DifficultyLevelExplanation/DifficultyLevelExplanation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\DifficultyLevelExplanation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F54EAC7F-0400-48D6-BA85-9532BB02D00E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A131BC96-8EDD-477C-B71F-67658558AAF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -137,13 +137,14 @@
     <t>explanationSizePortuguese</t>
   </si>
   <si>
+    <t>Um nível de dificuldade intermediário com um desafio considerável.</t>
+  </si>
+  <si>
+    <t>Um nível de dificuldade para jogadores avançados, que será difícil até para quem domina jogos de ação 3D. Você vai se arrepender de ter tentado.</t>
+  </si>
+  <si>
     <t>Um nível de dificuldade para iniciantes, pensado para que até quem não é bom em jogos de ação 3D possa se divertir.</t>
-  </si>
-  <si>
-    <t>Um nível de dificuldade intermediário com um desafio considerável.</t>
-  </si>
-  <si>
-    <t>Um nível de dificuldade para jogadores avançados, que será difícil até para quem domina jogos de ação 3D. Você vai se arrepender de ter tentado.</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -198,7 +199,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -211,10 +212,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -512,7 +509,7 @@
     <col min="13" max="13" width="24.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="56.25">
+    <row r="1" spans="1:13">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -546,10 +543,10 @@
       <c r="K1" t="s">
         <v>22</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="L1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="M1" t="s">
         <v>27</v>
       </c>
     </row>
@@ -557,10 +554,8 @@
       <c r="A2">
         <v>0</v>
       </c>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
     </row>
-    <row r="3" spans="1:13" ht="262.5">
+    <row r="3" spans="1:13" ht="131.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -594,14 +589,14 @@
       <c r="K3">
         <v>10</v>
       </c>
-      <c r="L3" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="M3" s="6">
+      <c r="L3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M3">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="187.5">
+    <row r="4" spans="1:13" ht="56.25">
       <c r="A4">
         <v>2</v>
       </c>
@@ -635,10 +630,10 @@
       <c r="K4">
         <v>14</v>
       </c>
-      <c r="L4" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="M4" s="6">
+      <c r="L4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="M4">
         <v>14</v>
       </c>
     </row>
@@ -676,10 +671,10 @@
       <c r="K5">
         <v>14</v>
       </c>
-      <c r="L5" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="M5" s="6">
+      <c r="L5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="M5">
         <v>14</v>
       </c>
     </row>
